--- a/DateBase/orders/Dang Nguyen48_2026-4-23.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-23.xlsx
@@ -801,6 +801,9 @@
       <c r="G2" t="str">
         <v>0531051051555551055545801001510656851012203030302010105</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
